--- a/artfynd/A 49938-2021 artfynd.xlsx
+++ b/artfynd/A 49938-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49938-2021 artfynd.xlsx
+++ b/artfynd/A 49938-2021 artfynd.xlsx
@@ -675,51 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96367164</v>
+        <v>96384531</v>
       </c>
       <c r="B2" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627100.4306924512</v>
+        <v>627072</v>
       </c>
       <c r="R2" t="n">
-        <v>7022394.134355434</v>
+        <v>7022581</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +742,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96367168</v>
+        <v>96382844</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627101.3661807616</v>
+        <v>627164</v>
       </c>
       <c r="R3" t="n">
-        <v>7022393.271275506</v>
+        <v>7022630</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,22 +850,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,37 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96381012</v>
+        <v>96379866</v>
       </c>
       <c r="B4" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627175.3777739739</v>
+        <v>627157</v>
       </c>
       <c r="R4" t="n">
-        <v>7022641.020999634</v>
+        <v>7022598</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96379706</v>
+        <v>96378977</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627135.255114638</v>
+        <v>627106</v>
       </c>
       <c r="R5" t="n">
-        <v>7022584.529429572</v>
+        <v>7022481</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,37 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96383190</v>
+        <v>96367164</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627149.9735943944</v>
+        <v>627100</v>
       </c>
       <c r="R6" t="n">
-        <v>7022656.665612327</v>
+        <v>7022394</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,22 +1174,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,37 +1216,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96384351</v>
+        <v>96379071</v>
       </c>
       <c r="B7" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1179</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627115.9896619492</v>
+        <v>627112</v>
       </c>
       <c r="R7" t="n">
-        <v>7022604.467870073</v>
+        <v>7022484</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,7 +1287,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1297,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96379866</v>
+        <v>96378981</v>
       </c>
       <c r="B8" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1335,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627156.80363588</v>
+        <v>627106</v>
       </c>
       <c r="R8" t="n">
-        <v>7022597.983368289</v>
+        <v>7022481</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1429,7 +1395,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1405,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96382017</v>
+        <v>96380002</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627164.5566937191</v>
+        <v>627169</v>
       </c>
       <c r="R9" t="n">
-        <v>7022629.791973216</v>
+        <v>7022613</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1542,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,56 +1540,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96383525</v>
+        <v>96380302</v>
       </c>
       <c r="B10" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627142.7724940636</v>
+        <v>627173</v>
       </c>
       <c r="R10" t="n">
-        <v>7022690.581542657</v>
+        <v>7022612</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,37 +1648,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96383120</v>
+        <v>96381833</v>
       </c>
       <c r="B11" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627152.4189212807</v>
+        <v>627176</v>
       </c>
       <c r="R11" t="n">
-        <v>7022651.812257069</v>
+        <v>7022641</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,15 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96384531</v>
+        <v>96383190</v>
       </c>
       <c r="B12" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,36 +1767,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>627072.3178198353</v>
+        <v>627150</v>
       </c>
       <c r="R12" t="n">
-        <v>7022580.688157227</v>
+        <v>7022657</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1887,7 +1827,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1837,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,15 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96380002</v>
+        <v>96383569</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>627169.7321469118</v>
+        <v>627147</v>
       </c>
       <c r="R13" t="n">
-        <v>7022612.896112042</v>
+        <v>7022694</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2000,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2010,7 +1945,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,52 +1972,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96383116</v>
+        <v>96384879</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>627152.4189212807</v>
+        <v>627096</v>
       </c>
       <c r="R14" t="n">
-        <v>7022651.812257069</v>
+        <v>7022677</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2112,19 +2041,9 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,37 +2070,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96379071</v>
+        <v>96378973</v>
       </c>
       <c r="B15" t="n">
-        <v>89967</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1179</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2192,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>627112.1898321791</v>
+        <v>627103</v>
       </c>
       <c r="R15" t="n">
-        <v>7022484.158992403</v>
+        <v>7022473</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2227,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2237,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,15 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96380302</v>
+        <v>96381012</v>
       </c>
       <c r="B16" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,21 +2189,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2305,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>627173.8170983779</v>
+        <v>627176</v>
       </c>
       <c r="R16" t="n">
-        <v>7022612.157845743</v>
+        <v>7022641</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2340,7 +2249,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2259,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,15 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96383569</v>
+        <v>96383120</v>
       </c>
       <c r="B17" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,21 +2297,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2418,10 +2322,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>627146.7150093709</v>
+        <v>627152</v>
       </c>
       <c r="R17" t="n">
-        <v>7022693.437721906</v>
+        <v>7022652</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2453,7 +2357,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2463,7 +2367,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,15 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96384424</v>
+        <v>96383565</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,21 +2405,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2531,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>627115.9896619492</v>
+        <v>627145</v>
       </c>
       <c r="R18" t="n">
-        <v>7022604.467870073</v>
+        <v>7022701</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2566,7 +2465,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2475,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,19 +2502,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96383565</v>
+        <v>96384871</v>
       </c>
       <c r="B19" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2628,12 +2522,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2644,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>627144.6306817344</v>
+        <v>627094</v>
       </c>
       <c r="R19" t="n">
-        <v>7022700.55536213</v>
+        <v>7022667</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,15 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96379055</v>
+        <v>96384823</v>
       </c>
       <c r="B20" t="n">
-        <v>89851</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5467</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2757,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>627112.1898321791</v>
+        <v>627087</v>
       </c>
       <c r="R20" t="n">
-        <v>7022484.158992403</v>
+        <v>7022632</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2792,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2802,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,37 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96384823</v>
+        <v>96378871</v>
       </c>
       <c r="B21" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92283</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>2063</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2870,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>627086.5059549281</v>
+        <v>627109</v>
       </c>
       <c r="R21" t="n">
-        <v>7022632.102207541</v>
+        <v>7022467</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2905,7 +2789,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2915,7 +2799,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2942,51 +2826,51 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96382844</v>
+        <v>96383525</v>
       </c>
       <c r="B22" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>310</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>627164.5566937191</v>
+        <v>627142</v>
       </c>
       <c r="R22" t="n">
-        <v>7022629.791973216</v>
+        <v>7022690</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3018,7 +2902,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3028,7 +2912,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3055,15 +2939,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96378767</v>
+        <v>96379055</v>
       </c>
       <c r="B23" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92398</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,21 +2950,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>5467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3096,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>627096.002432729</v>
+        <v>627112</v>
       </c>
       <c r="R23" t="n">
-        <v>7022506.02020175</v>
+        <v>7022484</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3131,7 +3010,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,7 +3020,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,15 +3047,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96383497</v>
+        <v>96384351</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,21 +3058,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3209,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>627142.7724940636</v>
+        <v>627116</v>
       </c>
       <c r="R24" t="n">
-        <v>7022690.581542657</v>
+        <v>7022604</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3244,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3254,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,15 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96378981</v>
+        <v>96367168</v>
       </c>
       <c r="B25" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3297,21 +3166,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3322,10 +3191,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>627106.4472329062</v>
+        <v>627101</v>
       </c>
       <c r="R25" t="n">
-        <v>7022481.231445643</v>
+        <v>7022393</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3352,22 +3221,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3394,15 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96378977</v>
+        <v>96378767</v>
       </c>
       <c r="B26" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3410,21 +3274,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3435,10 +3299,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>627106.4472329062</v>
+        <v>627096</v>
       </c>
       <c r="R26" t="n">
-        <v>7022481.231445643</v>
+        <v>7022506</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3470,7 +3334,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3344,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,15 +3371,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96380125</v>
+        <v>96379706</v>
       </c>
       <c r="B27" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,10 +3407,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>627169.7321469118</v>
+        <v>627135</v>
       </c>
       <c r="R27" t="n">
-        <v>7022612.896112042</v>
+        <v>7022584</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3583,7 +3442,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3593,7 +3452,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3620,15 +3479,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96378878</v>
+        <v>96380125</v>
       </c>
       <c r="B28" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3636,21 +3490,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3661,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>627109.6982765525</v>
+        <v>627169</v>
       </c>
       <c r="R28" t="n">
-        <v>7022467.408845555</v>
+        <v>7022613</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3696,7 +3550,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3706,7 +3560,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3733,37 +3587,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96378871</v>
+        <v>96382017</v>
       </c>
       <c r="B29" t="n">
-        <v>89734</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2063</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3774,10 +3623,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>627109.6982765525</v>
+        <v>627164</v>
       </c>
       <c r="R29" t="n">
-        <v>7022467.408845555</v>
+        <v>7022630</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3809,7 +3658,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3668,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,15 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96381833</v>
+        <v>96384424</v>
       </c>
       <c r="B30" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3862,21 +3706,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3887,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>627175.3777739739</v>
+        <v>627116</v>
       </c>
       <c r="R30" t="n">
-        <v>7022641.020999634</v>
+        <v>7022604</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3922,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3932,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3959,15 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96378973</v>
+        <v>96383116</v>
       </c>
       <c r="B31" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,35 +3814,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>627103.6177299276</v>
+        <v>627152</v>
       </c>
       <c r="R31" t="n">
-        <v>7022473.01871449</v>
+        <v>7022652</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4035,7 +3875,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4045,7 +3885,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 49938-2021 artfynd.xlsx
+++ b/artfynd/A 49938-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96384531</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96378977</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96367164</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96379071</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96378981</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96378973</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96378871</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96379055</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96367168</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1753,6 +1803,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96378767</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1861,6 +1916,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96382844</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1969,6 +2029,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96379866</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2077,6 +2142,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96380002</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96380302</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2293,6 +2368,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96381833</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2401,6 +2481,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96383190</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2509,6 +2594,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96383569</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2607,6 +2697,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96384879</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2715,6 +2810,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96381012</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2823,6 +2923,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96383120</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2931,6 +3036,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96383565</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3039,6 +3149,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96384871</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3147,6 +3262,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96384823</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3260,6 +3380,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96383525</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3368,6 +3493,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96384351</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3476,6 +3606,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96379706</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3584,6 +3719,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96380125</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3692,6 +3832,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96382017</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3800,6 +3945,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96384424</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3909,8 +4059,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96383116</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>